--- a/src/billing/in/rates.xlsx
+++ b/src/billing/in/rates.xlsx
@@ -157,7 +157,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -274,7 +274,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>45</v>
